--- a/raw_datas/buoy/9-秋田/秋田-JP54U34G-秋田船川港2.xlsx
+++ b/raw_datas/buoy/9-秋田/秋田-JP54U34G-秋田船川港2.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10419"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\3_Nmea\3-1-海岸-ブイ‐古谷\chart_features_geojson\9-秋田\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tokudashintarou/Desktop/LDA_PP/raw_datas/buoy/9-秋田/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D9EB176E-D931-44DE-B22E-5A81D433C4FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69A2607E-4A56-CB43-9F26-2EC5B481A553}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{29182667-93F8-4F50-8ED8-5366EE83FEF3}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="20740" windowHeight="11160" xr2:uid="{29182667-93F8-4F50-8ED8-5366EE83FEF3}"/>
   </bookViews>
   <sheets>
-    <sheet name="BOYLAT_point" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
@@ -47,7 +47,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="19" x14ac:knownFonts="1">
+  <fonts count="19">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1013,9 +1013,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{53DBCEDD-7D8C-43E6-9B63-D6076EDA7B97}">
   <dimension ref="A1:N2"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="18"/>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:14">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1059,7 +1059,7 @@
         <v>39.746469099999999</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:14">
       <c r="A2" t="s">
         <v>0</v>
       </c>
